--- a/data/trans_bre/P1804_2016_2023-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1804_2016_2023-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 10,76</t>
+          <t>1,76; 10,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 6,5</t>
+          <t>-1,38; 6,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,19; 194,15</t>
+          <t>13,95; 190,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 103,04</t>
+          <t>-12,89; 88,98</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 10,12</t>
+          <t>1,89; 9,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 6,36</t>
+          <t>-2,28; 6,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,89; 314,26</t>
+          <t>26,04; 308,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 92,8</t>
+          <t>-20,48; 87,89</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 11,77</t>
+          <t>0,48; 11,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 12,99</t>
+          <t>-2,94; 7,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 218,47</t>
+          <t>4,43; 221,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 530,43</t>
+          <t>-34,67; 122,67</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>101,26%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,98</t>
+          <t>0,66; 5,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,06</t>
+          <t>2,1; 6,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 95,09</t>
+          <t>8,73; 99,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 143,0</t>
+          <t>37,08; 192,63</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,94</t>
+          <t>1,11; 6,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,28</t>
+          <t>-0,35; 5,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 156,27</t>
+          <t>13,64; 147,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 105,01</t>
+          <t>-7,97; 155,14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213,67%</t>
+          <t>207,31%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 6,07</t>
+          <t>-0,88; 5,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,09</t>
+          <t>-0,72; 5,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 166,31</t>
+          <t>-12,34; 160,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 1786,41</t>
+          <t>-33,02; 1727,14</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,0</t>
+          <t>2,25; 4,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,45</t>
+          <t>0,99; 3,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,48; 87,61</t>
+          <t>33,48; 86,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 75,44</t>
+          <t>14,4; 63,49</t>
         </is>
       </c>
     </row>
